--- a/figures/MNIST/tables/window_size/noise_0.0_delta_0.5/results.xlsx
+++ b/figures/MNIST/tables/window_size/noise_0.0_delta_0.5/results.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\MUNDataStream\figures\MNIST\tables\window_size\noise_0.0_delta_0.5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBEDBC0-F4C5-4D95-B80E-E100486E29A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4650" yWindow="5730" windowWidth="28800" windowHeight="15885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accuracy" sheetId="1" r:id="rId1"/>
     <sheet name="recovery_time" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>window_size</t>
   </si>
@@ -35,17 +41,14 @@
     <t>accuracy_recovery_time</t>
   </si>
   <si>
-    <t>mean_memory</t>
-  </si>
-  <si>
     <t>mean_time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,17 +107,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -152,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -186,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,9 +232,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,7 +426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -424,24 +437,24 @@
         <v>0.8717521367521367</v>
       </c>
       <c r="D2">
-        <v>0.911867088607595</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.91186708860759502</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.8949203821656052</v>
+        <v>0.89492038216560521</v>
       </c>
       <c r="C3">
         <v>0.8733653846153846</v>
       </c>
       <c r="D3">
-        <v>0.9162025316455695</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0.91620253164556953</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -449,55 +462,55 @@
         <v>0.902776008492569</v>
       </c>
       <c r="C4">
-        <v>0.885534188034188</v>
+        <v>0.88553418803418804</v>
       </c>
       <c r="D4">
-        <v>0.9197995780590718</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>0.91979957805907175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.9056475583864119</v>
+        <v>0.90564755838641187</v>
       </c>
       <c r="C5">
-        <v>0.8940811965811966</v>
+        <v>0.89408119658119656</v>
       </c>
       <c r="D5">
         <v>0.9170675105485232</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.9134341825902336</v>
+        <v>0.91343418259023357</v>
       </c>
       <c r="C6">
-        <v>0.906474358974359</v>
+        <v>0.90647435897435902</v>
       </c>
       <c r="D6">
-        <v>0.9203059071729959</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.92030590717299587</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.9189278131634819</v>
+        <v>0.91892781316348193</v>
       </c>
       <c r="C7">
-        <v>0.9133012820512819</v>
+        <v>0.91330128205128192</v>
       </c>
       <c r="D7">
-        <v>0.9244831223628693</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>0.92448312236286934</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
@@ -505,27 +518,27 @@
         <v>0.9178715498938429</v>
       </c>
       <c r="C8">
-        <v>0.9117841880341881</v>
+        <v>0.91178418803418815</v>
       </c>
       <c r="D8">
-        <v>0.9238818565400843</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>0.92388185654008426</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.9173195329087049</v>
+        <v>0.91731953290870494</v>
       </c>
       <c r="C9">
-        <v>0.9106517094017093</v>
+        <v>0.91065170940170925</v>
       </c>
       <c r="D9">
-        <v>0.9239029535864979</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>0.92390295358649788</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -533,66 +546,66 @@
         <v>0.9190127388535031</v>
       </c>
       <c r="C10">
-        <v>0.9172222222222223</v>
+        <v>0.91722222222222227</v>
       </c>
       <c r="D10">
-        <v>0.9207805907172996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>0.92078059071729956</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.9083704883227176</v>
+        <v>0.90837048832271761</v>
       </c>
       <c r="C11">
         <v>0.9226388888888889</v>
       </c>
       <c r="D11">
-        <v>0.8942827004219409</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>0.89428270042194091</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.924644373673036</v>
+        <v>0.92464437367303598</v>
       </c>
       <c r="C12">
-        <v>0.9223076923076923</v>
+        <v>0.92230769230769227</v>
       </c>
       <c r="D12">
-        <v>0.926951476793249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.92695147679324896</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.924447983014862</v>
+        <v>0.92444798301486197</v>
       </c>
       <c r="C13">
-        <v>0.9257051282051281</v>
+        <v>0.92570512820512807</v>
       </c>
       <c r="D13">
-        <v>0.9232067510548524</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>0.92320675105485239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.8137154989384289</v>
+        <v>0.81371549893842887</v>
       </c>
       <c r="C14">
-        <v>0.8802029914529914</v>
+        <v>0.88020299145299141</v>
       </c>
       <c r="D14">
-        <v>0.7480696202531646</v>
+        <v>0.74806962025316459</v>
       </c>
     </row>
   </sheetData>
@@ -601,11 +614,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,11 +628,8 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -627,13 +637,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>2497611.464968153</v>
-      </c>
-      <c r="D2">
         <v>3.746902747305731</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
@@ -641,13 +648,10 @@
         <v>5.333333333333333</v>
       </c>
       <c r="C3">
-        <v>3117019.108280255</v>
-      </c>
-      <c r="D3">
-        <v>3.716315166519104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>3.7163151665191041</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -655,13 +659,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>3734428.662420382</v>
-      </c>
-      <c r="D4">
-        <v>3.692340109839696</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>3.6923401098396962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -669,27 +670,21 @@
         <v>7.333333333333333</v>
       </c>
       <c r="C5">
-        <v>4349840.127388535</v>
-      </c>
-      <c r="D5">
-        <v>3.645165784254781</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.6451657842547811</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>9.666666666666666</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="C6">
-        <v>4963253.503184713</v>
-      </c>
-      <c r="D6">
-        <v>3.646355997283434</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>3.6463559972834338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
@@ -697,13 +692,10 @@
         <v>7.333333333333333</v>
       </c>
       <c r="C7">
-        <v>5574668.789808917</v>
-      </c>
-      <c r="D7">
-        <v>3.694269516505308</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>3.6942695165053081</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
@@ -711,13 +703,10 @@
         <v>6.666666666666667</v>
       </c>
       <c r="C8">
-        <v>6184085.987261146</v>
-      </c>
-      <c r="D8">
-        <v>3.667396476234606</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>3.6673964762346061</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
@@ -725,13 +714,10 @@
         <v>5.333333333333333</v>
       </c>
       <c r="C9">
-        <v>6791505.0955414</v>
-      </c>
-      <c r="D9">
         <v>3.618397875842891</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -739,13 +725,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>7396926.11464968</v>
-      </c>
-      <c r="D10">
         <v>3.640387051228243</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -753,13 +736,10 @@
         <v>17</v>
       </c>
       <c r="C11">
-        <v>8000349.044585987</v>
-      </c>
-      <c r="D11">
-        <v>3.660444509083874</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>3.6604445090838742</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -767,27 +747,21 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>8601773.885350319</v>
-      </c>
-      <c r="D12">
-        <v>3.577574898245228</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>3.5775748982452278</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>8.333333333333334</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="C13">
-        <v>9201200.636942675</v>
-      </c>
-      <c r="D13">
-        <v>3.591293837785573</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>3.5912938377855732</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -795,10 +769,7 @@
         <v>17</v>
       </c>
       <c r="C14">
-        <v>8601773.885350319</v>
-      </c>
-      <c r="D14">
-        <v>6.660957198377917</v>
+        <v>6.6609571983779174</v>
       </c>
     </row>
   </sheetData>
